--- a/development/backend/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/backend/src/main/resources/templates/excel/riders-template.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="라이더 등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라이더 등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,13 +498,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -528,11 +529,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>직무 *
+(라이더 / 클리너)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>교육이수 *
 (온라인 / 오프라인 / 미완료)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>팀
 (선택)</t>

--- a/development/backend/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/backend/src/main/resources/templates/excel/riders-template.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:F500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -506,6 +506,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -535,11 +536,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>등급
+(초보 / 고수 / 미판정)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>교육이수 *
 (온라인 / 오프라인 / 미완료)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>팀
 (선택)</t>
